--- a/artfynd/A 61183-2025 artfynd.xlsx
+++ b/artfynd/A 61183-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AY21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,48 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>134707797</v>
+        <v>134746173</v>
       </c>
       <c r="B2" t="n">
-        <v>79373</v>
+        <v>79405</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Tallberget, Tallberget, Dlr</t>
+          <t>Tallsjön, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>488383</v>
+        <v>488362</v>
       </c>
       <c r="R2" t="n">
-        <v>6823713</v>
+        <v>6823715</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -743,9 +743,19 @@
           <t>2026-06-27</t>
         </is>
       </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>21:24</t>
+        </is>
+      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>21:24</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -760,60 +770,71 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>134707884</v>
+        <v>134746163</v>
       </c>
       <c r="B3" t="n">
-        <v>79373</v>
+        <v>93271</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Husknoppen, Husknoppen, Dlr</t>
+          <t>Tallsjön, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>488377</v>
+        <v>488302</v>
       </c>
       <c r="R3" t="n">
-        <v>6823767</v>
+        <v>6823699</v>
       </c>
       <c r="S3" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -840,36 +861,47 @@
           <t>2026-06-27</t>
         </is>
       </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>21:33</t>
+        </is>
+      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2026-06-27</t>
         </is>
       </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>21:33</t>
+        </is>
+      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>134707906</v>
+        <v>134707797</v>
       </c>
       <c r="B4" t="n">
         <v>79373</v>
@@ -900,17 +932,17 @@
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Husknoppen, Husknoppen, Dlr</t>
+          <t>Tallberget, Tallberget, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>488358</v>
+        <v>488383</v>
       </c>
       <c r="R4" t="n">
-        <v>6823775</v>
+        <v>6823713</v>
       </c>
       <c r="S4" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -954,19 +986,19 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>134708065</v>
+        <v>134707884</v>
       </c>
       <c r="B5" t="n">
         <v>79373</v>
@@ -1001,10 +1033,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>488355</v>
+        <v>488377</v>
       </c>
       <c r="R5" t="n">
-        <v>6823809</v>
+        <v>6823767</v>
       </c>
       <c r="S5" t="n">
         <v>20</v>
@@ -1063,7 +1095,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>134708115</v>
+        <v>134707906</v>
       </c>
       <c r="B6" t="n">
         <v>79373</v>
@@ -1098,13 +1130,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>488355</v>
+        <v>488358</v>
       </c>
       <c r="R6" t="n">
-        <v>6823808</v>
+        <v>6823775</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1160,7 +1192,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>134708155</v>
+        <v>134708065</v>
       </c>
       <c r="B7" t="n">
         <v>79373</v>
@@ -1195,10 +1227,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>488335</v>
+        <v>488355</v>
       </c>
       <c r="R7" t="n">
-        <v>6823807</v>
+        <v>6823809</v>
       </c>
       <c r="S7" t="n">
         <v>20</v>
@@ -1257,32 +1289,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>134708006</v>
+        <v>134708115</v>
       </c>
       <c r="B8" t="n">
-        <v>79131</v>
+        <v>79373</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1292,10 +1324,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>488330</v>
+        <v>488355</v>
       </c>
       <c r="R8" t="n">
-        <v>6823786</v>
+        <v>6823808</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1354,48 +1386,48 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>134708246</v>
+        <v>134708155</v>
       </c>
       <c r="B9" t="n">
-        <v>79131</v>
+        <v>79373</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Tallberget, Tallberget, Dlr</t>
+          <t>Husknoppen, Husknoppen, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>488337</v>
+        <v>488335</v>
       </c>
       <c r="R9" t="n">
-        <v>6823774</v>
+        <v>6823807</v>
       </c>
       <c r="S9" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1448,6 +1480,1285 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>134746170</v>
+      </c>
+      <c r="B10" t="n">
+        <v>79373</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Tallsjön, Dlr</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>488340</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6823723</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>21:26</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>21:26</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>134746171</v>
+      </c>
+      <c r="B11" t="n">
+        <v>79373</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Tallsjön, Dlr</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>488349</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6823722</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>21:25</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>21:25</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>134746172</v>
+      </c>
+      <c r="B12" t="n">
+        <v>79373</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Tallsjön, Dlr</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>488354</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6823718</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>21:25</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>21:25</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>134746166</v>
+      </c>
+      <c r="B13" t="n">
+        <v>79130</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Tallsjön, Dlr</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>488315</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6823708</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>21:30</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>21:30</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>134746169</v>
+      </c>
+      <c r="B14" t="n">
+        <v>79992</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Tallsjön, Dlr</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>488324</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6823697</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>21:28</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>21:28</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>134746164</v>
+      </c>
+      <c r="B15" t="n">
+        <v>57162</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Tallsjön, Dlr</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>488304</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6823698</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>21:32</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>21:32</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>134746165</v>
+      </c>
+      <c r="B16" t="n">
+        <v>57162</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Tallsjön, Dlr</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>488307</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6823709</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>21:31</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>21:31</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>134746174</v>
+      </c>
+      <c r="B17" t="n">
+        <v>57162</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Tallsjön, Dlr</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>488369</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6823714</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>21:23</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>21:23</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>134708006</v>
+      </c>
+      <c r="B18" t="n">
+        <v>79131</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Husknoppen, Husknoppen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>488330</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6823786</v>
+      </c>
+      <c r="S18" t="n">
+        <v>25</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>134708246</v>
+      </c>
+      <c r="B19" t="n">
+        <v>79131</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Tallberget, Tallberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>488337</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6823774</v>
+      </c>
+      <c r="S19" t="n">
+        <v>25</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>134746167</v>
+      </c>
+      <c r="B20" t="n">
+        <v>79131</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Tallsjön, Dlr</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>488315</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6823708</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>21:30</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>21:30</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>134746168</v>
+      </c>
+      <c r="B21" t="n">
+        <v>79963</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Tallsjön, Dlr</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>488315</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6823709</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>21:29</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>21:29</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 61183-2025 artfynd.xlsx
+++ b/artfynd/A 61183-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY21"/>
+  <dimension ref="A1:AZ21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134746173</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -898,6 +908,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134746163</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -995,6 +1010,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134707797</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1092,6 +1112,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134707884</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1189,6 +1214,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134707906</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1286,6 +1316,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134708065</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1383,6 +1418,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134708115</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1480,6 +1520,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134708155</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1587,6 +1632,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134746170</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1694,6 +1744,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134746171</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1801,6 +1856,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134746172</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1908,6 +1968,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134746166</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2015,6 +2080,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134746169</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2127,6 +2197,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134746164</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2239,6 +2314,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134746165</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2351,6 +2431,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134746174</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2448,6 +2533,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134708006</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2545,6 +2635,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134708246</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2652,6 +2747,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134746167</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2759,8 +2859,35 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134746168</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>